--- a/artfynd/A 26684-2023 artfynd.xlsx
+++ b/artfynd/A 26684-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26684-2023 artfynd.xlsx
+++ b/artfynd/A 26684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112469861</v>
+        <v>112469693</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö om Hjälmbergsberget, Sm</t>
+          <t>Kontinuitetsskog N om Hjälmbergsberget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487279</v>
+        <v>487213</v>
       </c>
       <c r="R2" t="n">
-        <v>6339015</v>
+        <v>6339316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,16 +787,11 @@
         <v>112469706</v>
       </c>
       <c r="B3" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487233</v>
+        <v>487234</v>
       </c>
       <c r="R3" t="n">
         <v>6339335</v>
@@ -904,50 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112469693</v>
+        <v>112469735</v>
       </c>
       <c r="B4" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487213</v>
+        <v>487235</v>
       </c>
       <c r="R4" t="n">
-        <v>6339317</v>
+        <v>6339400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,6 +1000,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112469861</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö om Hjälmbergsberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487279</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6339015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26684-2023 artfynd.xlsx
+++ b/artfynd/A 26684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112469693</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112469706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112469735</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,8 +1130,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112469861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>